--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Value Discovery Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Value Discovery Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="229">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Value Discovery Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -52,7 +52,7 @@
     <t>Yield to Call @</t>
   </si>
   <si>
-    <t>Equity &amp; Equity Related Instruments (Note -1)</t>
+    <t>Equity &amp; Equity Related Instruments</t>
   </si>
   <si>
     <t/>
@@ -88,6 +88,12 @@
     <t>Petroleum Products</t>
   </si>
   <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
     <t>Infosys Ltd.</t>
   </si>
   <si>
@@ -106,10 +112,10 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
   </si>
   <si>
     <t>Maruti Suzuki India Ltd.</t>
@@ -121,10 +127,31 @@
     <t>Automobiles</t>
   </si>
   <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
   </si>
   <si>
     <t>Hindustan Unilever Ltd.</t>
@@ -133,16 +160,25 @@
     <t>INE030A01027</t>
   </si>
   <si>
-    <t>Diversified Fmcg</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE467B01029</t>
   </si>
   <si>
     <t>Oil &amp; Natural Gas Corporation Ltd.</t>
@@ -154,30 +190,6 @@
     <t>Oil</t>
   </si>
   <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>SBI Life Insurance Company Ltd.</t>
   </si>
   <si>
@@ -187,16 +199,58 @@
     <t>Insurance</t>
   </si>
   <si>
+    <t>Max Financial Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE180A01020</t>
+  </si>
+  <si>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
     <t>Tata Motors Ltd.</t>
   </si>
   <si>
     <t>INE155A01022</t>
   </si>
   <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
+    <t>Dabur India Ltd.</t>
+  </si>
+  <si>
+    <t>INE016A01026</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Hero Motocorp Ltd.</t>
+  </si>
+  <si>
+    <t>INE158A01026</t>
+  </si>
+  <si>
+    <t>TVS Motor Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE494B01023</t>
+  </si>
+  <si>
+    <t>Lupin Ltd.</t>
+  </si>
+  <si>
+    <t>INE326A01037</t>
+  </si>
+  <si>
+    <t>Life Insurance Corporation of India</t>
+  </si>
+  <si>
+    <t>INE0J1Y01017</t>
   </si>
   <si>
     <t>HDFC Life Insurance Company Ltd.</t>
@@ -205,25 +259,13 @@
     <t>INE795G01014</t>
   </si>
   <si>
-    <t>Dabur India Ltd.</t>
-  </si>
-  <si>
-    <t>INE016A01026</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>Lupin Ltd.</t>
-  </si>
-  <si>
-    <t>INE326A01037</t>
-  </si>
-  <si>
-    <t>TVS Motor Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE494B01023</t>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
   </si>
   <si>
     <t>Tata Steel Ltd.</t>
@@ -235,84 +277,93 @@
     <t>Ferrous Metals</t>
   </si>
   <si>
+    <t>Ambuja Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE079A01024</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>LIC Housing Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE115A01026</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>HCL Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE860A01027</t>
+  </si>
+  <si>
+    <t>Aurobindo Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE406A01037</t>
+  </si>
+  <si>
+    <t>Gujarat State Petronet Ltd.</t>
+  </si>
+  <si>
+    <t>INE246F01010</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
+    <t>Asian Paints Ltd.</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Zydus Lifesciences Ltd.</t>
+  </si>
+  <si>
+    <t>INE010B01027</t>
+  </si>
+  <si>
+    <t>Bharat Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE029A01011</t>
+  </si>
+  <si>
+    <t>Cipla Ltd.</t>
+  </si>
+  <si>
+    <t>INE059A01026</t>
+  </si>
+  <si>
     <t>Bajaj Finserv Ltd.</t>
   </si>
   <si>
     <t>INE918I01026</t>
   </si>
   <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
-  </si>
-  <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Life Insurance Corporation of India</t>
-  </si>
-  <si>
-    <t>INE0J1Y01017</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>SBI Cards &amp; Payment Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE018E01016</t>
-  </si>
-  <si>
-    <t>HCL Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE860A01027</t>
-  </si>
-  <si>
-    <t>Aurobindo Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE406A01037</t>
-  </si>
-  <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Cipla Ltd.</t>
-  </si>
-  <si>
-    <t>INE059A01026</t>
-  </si>
-  <si>
     <t>UPL Ltd.</t>
   </si>
   <si>
@@ -322,34 +373,25 @@
     <t>Fertilizers &amp; Agrochemicals</t>
   </si>
   <si>
-    <t>Gujarat State Petronet Ltd.</t>
-  </si>
-  <si>
-    <t>INE246F01010</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
-  </si>
-  <si>
-    <t>Zydus Lifesciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE010B01027</t>
-  </si>
-  <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
+    <t>Adani Wilmar Ltd</t>
+  </si>
+  <si>
+    <t>INE699H01024</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
+    <t>Star Health &amp; Allied Insurance</t>
+  </si>
+  <si>
+    <t>INE575P01011</t>
+  </si>
+  <si>
+    <t>Bata India Ltd.</t>
+  </si>
+  <si>
+    <t>INE176A01028</t>
   </si>
   <si>
     <t>Hindalco Industries Ltd.</t>
@@ -361,37 +403,34 @@
     <t>Non - Ferrous Metals</t>
   </si>
   <si>
-    <t>Cholamandalam Investment And Finance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE121A01024</t>
-  </si>
-  <si>
-    <t>Adani Wilmar Ltd</t>
-  </si>
-  <si>
-    <t>INE699H01024</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>Max Financial Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE180A01020</t>
-  </si>
-  <si>
-    <t>Bata India Ltd.</t>
-  </si>
-  <si>
-    <t>INE176A01028</t>
-  </si>
-  <si>
-    <t>Star Health &amp; Allied Insurance</t>
-  </si>
-  <si>
-    <t>INE575P01011</t>
+    <t>Zee Entertainment Enterprises Ltd.</t>
+  </si>
+  <si>
+    <t>INE256A01028</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Wipro Ltd.</t>
+  </si>
+  <si>
+    <t>INE075A01022</t>
+  </si>
+  <si>
+    <t>Gland Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE068V01023</t>
+  </si>
+  <si>
+    <t>Tata Chemicals Ltd.</t>
+  </si>
+  <si>
+    <t>INE092A01019</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
   </si>
   <si>
     <t>ACC Ltd.</t>
@@ -400,31 +439,22 @@
     <t>INE012A01025</t>
   </si>
   <si>
-    <t>LIC Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE115A01026</t>
-  </si>
-  <si>
-    <t>Gland Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE068V01023</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>Indian Bank</t>
-  </si>
-  <si>
-    <t>INE562A01011</t>
+    <t>Alkem Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE540L01014</t>
+  </si>
+  <si>
+    <t>Galaxy Surfactants Ltd.</t>
+  </si>
+  <si>
+    <t>INE600K01018</t>
+  </si>
+  <si>
+    <t>TVS Holdings Ltd.</t>
+  </si>
+  <si>
+    <t>INE105A01035</t>
   </si>
   <si>
     <t>The Great Eastern Shipping Company Ltd.</t>
@@ -433,6 +463,36 @@
     <t>INE017A01032</t>
   </si>
   <si>
+    <t>IndusInd Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE095A01012</t>
+  </si>
+  <si>
+    <t>Gateway Distriparks Ltd.</t>
+  </si>
+  <si>
+    <t>INE079J01017</t>
+  </si>
+  <si>
+    <t>Kalpataru Projects International Ltd</t>
+  </si>
+  <si>
+    <t>INE220B01022</t>
+  </si>
+  <si>
+    <t>JK Lakshmi Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE786A01032</t>
+  </si>
+  <si>
+    <t>PVR INOX Ltd.</t>
+  </si>
+  <si>
+    <t>INE191H01014</t>
+  </si>
+  <si>
     <t>Zydus Wellness Ltd.</t>
   </si>
   <si>
@@ -442,21 +502,6 @@
     <t>Food Products</t>
   </si>
   <si>
-    <t>Tata Chemicals Ltd.</t>
-  </si>
-  <si>
-    <t>INE092A01019</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Gateway Distriparks Ltd.</t>
-  </si>
-  <si>
-    <t>INE079J01017</t>
-  </si>
-  <si>
     <t>Coal India Ltd.</t>
   </si>
   <si>
@@ -466,33 +511,6 @@
     <t>Consumable Fuels</t>
   </si>
   <si>
-    <t>Zee Entertainment Enterprises Ltd.</t>
-  </si>
-  <si>
-    <t>INE256A01028</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>TVS Holdings Ltd.</t>
-  </si>
-  <si>
-    <t>INE105A01035</t>
-  </si>
-  <si>
-    <t>Kalpataru Projects International Ltd</t>
-  </si>
-  <si>
-    <t>INE220B01022</t>
-  </si>
-  <si>
-    <t>PVR INOX Ltd.</t>
-  </si>
-  <si>
-    <t>INE191H01014</t>
-  </si>
-  <si>
     <t>Ttk Prestige Ltd.</t>
   </si>
   <si>
@@ -505,42 +523,30 @@
     <t>INE844O01030</t>
   </si>
   <si>
-    <t>Alkem Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE540L01014</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE095A01012</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd. - Partly Paid Share</t>
-  </si>
-  <si>
-    <t>IN9397D01014</t>
-  </si>
-  <si>
     <t>UPL Ltd. (Right Share)</t>
   </si>
   <si>
-    <t>IN9628A01018</t>
+    <t>IN9628A01026</t>
+  </si>
+  <si>
+    <t>V-Guard Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE951I01027</t>
   </si>
   <si>
     <t>Foreign Securities/Overseas ETFs</t>
   </si>
   <si>
+    <t>Viatris Inc.</t>
+  </si>
+  <si>
+    <t>US92556V1061</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
     <t>Vodafone Group Plc - SP ADR</t>
   </si>
   <si>
@@ -550,24 +556,6 @@
     <t>Wireless Telecommunication Services</t>
   </si>
   <si>
-    <t>Viatris Inc.</t>
-  </si>
-  <si>
-    <t>US92556V1061</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>British American Tobacco PLC</t>
-  </si>
-  <si>
-    <t>US1104481072</t>
-  </si>
-  <si>
-    <t>Tobacco</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -595,10 +583,7 @@
     <t>Certificate of Deposits</t>
   </si>
   <si>
-    <t>Small Industries Development Bank Of India.</t>
-  </si>
-  <si>
-    <t>INE556F16AQ6</t>
+    <t>INE238AD6900</t>
   </si>
   <si>
     <t>CRISIL A1+</t>
@@ -607,58 +592,34 @@
     <t>Punjab National Bank</t>
   </si>
   <si>
-    <t>INE160A16PK9</t>
-  </si>
-  <si>
-    <t>NABARD **</t>
-  </si>
-  <si>
-    <t>INE261F16785</t>
-  </si>
-  <si>
-    <t>Union Bank Of India **</t>
-  </si>
-  <si>
-    <t>INE692A16GY1</t>
-  </si>
-  <si>
-    <t>ICRA A1+</t>
-  </si>
-  <si>
-    <t>INE261F16835</t>
-  </si>
-  <si>
-    <t>INE160A16OM8</t>
+    <t>INE160A16RG3</t>
   </si>
   <si>
     <t>Commercial Papers</t>
   </si>
   <si>
-    <t>Reliance Retail Ventures Ltd</t>
-  </si>
-  <si>
-    <t>INE929O14CP0</t>
-  </si>
-  <si>
-    <t>Toyota Financial Services India **</t>
-  </si>
-  <si>
-    <t>INE692Q14BN6</t>
+    <t>Sikka Ports &amp; Terminals Ltd. **</t>
+  </si>
+  <si>
+    <t>INE941D14667</t>
+  </si>
+  <si>
+    <t>Kotak Securities Ltd. **</t>
+  </si>
+  <si>
+    <t>INE028E14QJ5</t>
   </si>
   <si>
     <t>Reliance Retail Ventures Ltd **</t>
   </si>
   <si>
-    <t>INE929O14CT2</t>
-  </si>
-  <si>
-    <t>INE929O14CS4</t>
-  </si>
-  <si>
-    <t>Barclays Investments &amp; Loans (India) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE704I14IK7</t>
+    <t>INE929O14DF9</t>
+  </si>
+  <si>
+    <t>Titan Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE280A14419</t>
   </si>
   <si>
     <t>Treasury Bills</t>
@@ -667,37 +628,28 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X383</t>
+    <t>IN002024X490</t>
   </si>
   <si>
     <t>SOV</t>
   </si>
   <si>
-    <t>IN002024X417</t>
-  </si>
-  <si>
-    <t>IN002024X409</t>
-  </si>
-  <si>
-    <t>182 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002024Y191</t>
-  </si>
-  <si>
-    <t>IN002024X425</t>
-  </si>
-  <si>
-    <t>IN002024Y225</t>
-  </si>
-  <si>
     <t>364 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024Z040</t>
-  </si>
-  <si>
-    <t>^</t>
+    <t>IN002024Z198</t>
+  </si>
+  <si>
+    <t>IN002025X059</t>
+  </si>
+  <si>
+    <t>IN002025X026</t>
+  </si>
+  <si>
+    <t>IN002025X034</t>
+  </si>
+  <si>
+    <t>IN002024Z115</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -721,36 +673,12 @@
     <t>Total Net Assets</t>
   </si>
   <si>
-    <t>Details of Stock Future / Index Future</t>
-  </si>
-  <si>
-    <t>Stock / Index Futures</t>
-  </si>
-  <si>
-    <t>Bata India Ltd. $$</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd. $$</t>
-  </si>
-  <si>
-    <t>SBI Cards and Payment Services Ltd. $$</t>
-  </si>
-  <si>
-    <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
     <t>** Non Traded / Illiquid Securities.</t>
   </si>
   <si>
-    <t>$$ - Derivatives.</t>
-  </si>
-  <si>
-    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
-  </si>
-  <si>
     <t>Industry classification is done as per Global Industry Classification Standard (GICS) by MSCI and Standard &amp; Poor’s for Foreign Equity</t>
   </si>
   <si>
@@ -763,7 +691,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -773,20 +701,16 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benchmark name - NIFTY 500 TRI </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="177" formatCode="##0.00"/>
     <numFmt numFmtId="178" formatCode="##0.00%"/>
-    <numFmt numFmtId="179" formatCode="\^"/>
-    <numFmt numFmtId="180" formatCode="##0"/>
+    <numFmt numFmtId="179" formatCode="##0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -990,7 +914,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1042,7 +966,7 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -1051,10 +975,6 @@
       <protection/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -1172,13 +1092,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>168</xdr:row>
+      <xdr:row>147</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>178</xdr:row>
+      <xdr:row>157</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1196,8 +1116,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="32461200"/>
-          <a:ext cx="3810000" cy="1905000"/>
+          <a:off x="666750" y="28460700"/>
+          <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1211,13 +1131,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>183</xdr:row>
+      <xdr:row>162</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>193</xdr:row>
+      <xdr:row>172</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1235,8 +1155,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="35318700"/>
-          <a:ext cx="3810000" cy="1905000"/>
+          <a:off x="666750" y="31318200"/>
+          <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1569,19 +1489,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J182"/>
+  <dimension ref="B1:J160"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="57.142857142857146" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="17.142857142857142" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="11.142857142857142" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="22" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="17.142857142857142" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.142857142857142" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="21" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1669,10 +1589,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>4507996.239999999</v>
+        <v>4882851.170000002</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9313984025519998</v>
+        <v>0.9283399992377</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1706,10 +1626,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>4507996.239999999</v>
+        <v>4882851.170000002</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9313984025519998</v>
+        <v>0.9283399992377</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1743,10 +1663,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>4349271.56</v>
+        <v>4778816.780000002</v>
       </c>
       <c r="H9" s="10">
-        <v>0.8986042506655998</v>
+        <v>0.9085607182049</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1769,13 +1689,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="14">
-        <v>22504621</v>
+        <v>19906221</v>
       </c>
       <c r="G10" s="15">
-        <v>382297.25</v>
+        <v>387156.09</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0789865450179</v>
+        <v>0.073607093844</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1801,10 +1721,10 @@
         <v>25469866</v>
       </c>
       <c r="G11" s="15">
-        <v>319086.48</v>
+        <v>368243.32</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0659265496079</v>
+        <v>0.0700113502352</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1827,13 +1747,13 @@
         <v>23</v>
       </c>
       <c r="F12" s="14">
-        <v>23927019</v>
+        <v>25843799</v>
       </c>
       <c r="G12" s="15">
-        <v>302700.72</v>
+        <v>367214.54</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0625410830112</v>
+        <v>0.0698157559827</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1853,16 +1773,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F13" s="14">
-        <v>14161378</v>
+        <v>21071023</v>
       </c>
       <c r="G13" s="15">
-        <v>266205.58</v>
+        <v>251208.74</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0550008116163</v>
+        <v>0.047760440239</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1873,25 +1793,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="F14" s="14">
-        <v>12594544</v>
+        <v>14705062</v>
       </c>
       <c r="G14" s="15">
-        <v>219642.55</v>
+        <v>229796</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0453804105664</v>
+        <v>0.0436893960185</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1902,25 +1822,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="D15" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>18</v>
-      </c>
       <c r="F15" s="14">
-        <v>20361911</v>
+        <v>12009044</v>
       </c>
       <c r="G15" s="15">
-        <v>200788.80</v>
+        <v>201463.72</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0414850318444</v>
+        <v>0.0383027913734</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1940,16 +1860,16 @@
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F16" s="14">
-        <v>1543016</v>
+        <v>24040123</v>
       </c>
       <c r="G16" s="15">
-        <v>189955.30</v>
+        <v>195277.92</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0392467192867</v>
+        <v>0.0371267314511</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1960,25 +1880,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>18</v>
-      </c>
       <c r="F17" s="14">
-        <v>20121002</v>
+        <v>1543016</v>
       </c>
       <c r="G17" s="15">
-        <v>155515.22</v>
+        <v>190084.14</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0321310444307</v>
+        <v>0.0361392768773</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -2001,13 +1921,13 @@
         <v>39</v>
       </c>
       <c r="F18" s="14">
-        <v>6281477</v>
+        <v>4360155</v>
       </c>
       <c r="G18" s="15">
-        <v>155077.10</v>
+        <v>160240.06</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0320405243312</v>
+        <v>0.0304652449971</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -2030,13 +1950,13 @@
         <v>42</v>
       </c>
       <c r="F19" s="14">
-        <v>9508281</v>
+        <v>33732006</v>
       </c>
       <c r="G19" s="15">
-        <v>154633.17</v>
+        <v>141016.65</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0319488038259</v>
+        <v>0.0268104417268</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -2059,13 +1979,13 @@
         <v>45</v>
       </c>
       <c r="F20" s="14">
-        <v>52693747</v>
+        <v>7439778</v>
       </c>
       <c r="G20" s="15">
-        <v>138379.05</v>
+        <v>138097.16</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0285905354076</v>
+        <v>0.0262553809129</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2085,16 +2005,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F21" s="14">
-        <v>36640718</v>
+        <v>5469820</v>
       </c>
       <c r="G21" s="15">
-        <v>118715.93</v>
+        <v>128447.78</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0245279325166</v>
+        <v>0.0244208164115</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2105,25 +2025,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>39</v>
-      </c>
       <c r="F22" s="14">
-        <v>26506914</v>
+        <v>38068580</v>
       </c>
       <c r="G22" s="15">
-        <v>118618.44</v>
+        <v>127110.99</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0245077900796</v>
+        <v>0.0241666625198</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2143,16 +2063,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="F23" s="14">
-        <v>2789823</v>
+        <v>9322942</v>
       </c>
       <c r="G23" s="15">
-        <v>99524.15</v>
+        <v>116648.65</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0205627133188</v>
+        <v>0.0221775360096</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2163,25 +2083,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>55</v>
-      </c>
       <c r="D24" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F24" s="14">
-        <v>6613677</v>
+        <v>3260168</v>
       </c>
       <c r="G24" s="15">
-        <v>98120.51</v>
+        <v>112912.66</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0202727068538</v>
+        <v>0.0214672401531</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2192,25 +2112,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>34</v>
-      </c>
       <c r="F25" s="14">
-        <v>12534575</v>
+        <v>46699529</v>
       </c>
       <c r="G25" s="15">
-        <v>89760.09</v>
+        <v>111798.67</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0185453580678</v>
+        <v>0.0212554455602</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2221,25 +2141,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="F26" s="14">
-        <v>6172827</v>
+        <v>5294832</v>
       </c>
       <c r="G26" s="15">
-        <v>75144.91</v>
+        <v>95952.95</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0155257115152</v>
+        <v>0.0182428172452</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2259,16 +2179,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F27" s="14">
-        <v>10982014</v>
+        <v>6052387</v>
       </c>
       <c r="G27" s="15">
-        <v>70070.74</v>
+        <v>90949.22</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0144773357889</v>
+        <v>0.0172914954575</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2291,13 +2211,13 @@
         <v>65</v>
       </c>
       <c r="F28" s="14">
-        <v>11166864</v>
+        <v>1613350</v>
       </c>
       <c r="G28" s="15">
-        <v>59167.63</v>
+        <v>85991.56</v>
       </c>
       <c r="H28" s="16">
-        <v>0.012224641089</v>
+        <v>0.0163489326145</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2317,16 +2237,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F29" s="14">
-        <v>2823402</v>
+        <v>10847725</v>
       </c>
       <c r="G29" s="15">
-        <v>58739.47</v>
+        <v>78049.38</v>
       </c>
       <c r="H29" s="16">
-        <v>0.012136178828</v>
+        <v>0.0148389452898</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2346,16 +2266,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F30" s="14">
-        <v>2318479</v>
+        <v>14370825</v>
       </c>
       <c r="G30" s="15">
-        <v>56985.90</v>
+        <v>69403.9</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0117738732249</v>
+        <v>0.0131952447924</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2366,25 +2286,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="F31" s="14">
-        <v>40827807</v>
+        <v>1468947</v>
       </c>
       <c r="G31" s="15">
-        <v>54962.39</v>
+        <v>63301.33</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0113557952405</v>
+        <v>0.012035008768</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2404,16 +2324,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="F32" s="14">
-        <v>2883047</v>
+        <v>2230537</v>
       </c>
       <c r="G32" s="15">
-        <v>50052.58</v>
+        <v>62026.77</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0103413779812</v>
+        <v>0.0117926862011</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2424,25 +2344,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F33" s="14">
-        <v>1113593</v>
+        <v>2823402</v>
       </c>
       <c r="G33" s="15">
-        <v>48320.47</v>
+        <v>55273.74</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0099835062348</v>
+        <v>0.0105087830784</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2453,25 +2373,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F34" s="14">
-        <v>9136716</v>
+        <v>5674985</v>
       </c>
       <c r="G34" s="15">
-        <v>46853.08</v>
+        <v>54164.89</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0096803283639</v>
+        <v>0.0102979657152</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2482,25 +2402,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F35" s="14">
-        <v>5203975</v>
+        <v>6954114</v>
       </c>
       <c r="G35" s="15">
-        <v>43997.01</v>
+        <v>54023.03</v>
       </c>
       <c r="H35" s="16">
-        <v>0.009090234918</v>
+        <v>0.0102709949337</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2511,25 +2431,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="F36" s="14">
-        <v>16313216</v>
+        <v>11234431</v>
       </c>
       <c r="G36" s="15">
-        <v>42593.81</v>
+        <v>48931.56</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0088003193615</v>
+        <v>0.0093029917955</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2540,25 +2460,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="D37" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>87</v>
-      </c>
       <c r="F37" s="14">
-        <v>1840132</v>
+        <v>30153616</v>
       </c>
       <c r="G37" s="15">
-        <v>42337.76</v>
+        <v>48553.35</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0087474167972</v>
+        <v>0.0092310855549</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2569,25 +2489,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="D38" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="F38" s="14">
-        <v>5226655</v>
+        <v>7467669</v>
       </c>
       <c r="G38" s="15">
-        <v>40673.83</v>
+        <v>41333.55</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0084036317403</v>
+        <v>0.0078584389406</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2607,16 +2527,16 @@
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="F39" s="14">
-        <v>2293816</v>
+        <v>1173383</v>
       </c>
       <c r="G39" s="15">
-        <v>39578.65</v>
+        <v>38347.33</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0081773562848</v>
+        <v>0.0072906912505</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2627,25 +2547,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="F40" s="14">
-        <v>3224384</v>
+        <v>6410157</v>
       </c>
       <c r="G40" s="15">
-        <v>37786.56</v>
+        <v>38233.38</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0078070920534</v>
+        <v>0.0072690267887</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2656,25 +2576,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="F41" s="14">
-        <v>1213146</v>
+        <v>2293816</v>
       </c>
       <c r="G41" s="15">
-        <v>35351.68</v>
+        <v>37540.59</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0073040207947</v>
+        <v>0.0071373118038</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2685,25 +2605,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F42" s="14">
-        <v>2366964</v>
+        <v>3230588</v>
       </c>
       <c r="G42" s="15">
-        <v>35016.87</v>
+        <v>37080.69</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0072348456041</v>
+        <v>0.007049874454</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2714,25 +2634,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F43" s="14">
-        <v>5684590</v>
+        <v>9668656</v>
       </c>
       <c r="G43" s="15">
-        <v>34320.71</v>
+        <v>31790.54</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0070910117858</v>
+        <v>0.0060440977723</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2743,25 +2663,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="F44" s="14">
-        <v>9690699</v>
+        <v>1691476</v>
       </c>
       <c r="G44" s="15">
-        <v>33500.75</v>
+        <v>31721.94</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0069215996139</v>
+        <v>0.006031055367</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2781,16 +2701,16 @@
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="F45" s="14">
-        <v>1691476</v>
+        <v>1398537</v>
       </c>
       <c r="G45" s="15">
-        <v>31436.08</v>
+        <v>31594.35</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0064950175501</v>
+        <v>0.0060067976339</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2801,25 +2721,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F46" s="14">
-        <v>2806584</v>
+        <v>3335980</v>
       </c>
       <c r="G46" s="15">
-        <v>27230.88</v>
+        <v>31024.61</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0056261799659</v>
+        <v>0.0058984772259</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2830,25 +2750,25 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="F47" s="14">
-        <v>621819</v>
+        <v>9531551</v>
       </c>
       <c r="G47" s="15">
-        <v>26889.63</v>
+        <v>30348.46</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0055556742051</v>
+        <v>0.0057699258798</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2868,16 +2788,16 @@
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="F48" s="14">
-        <v>4391044</v>
+        <v>1825845</v>
       </c>
       <c r="G48" s="15">
-        <v>26095.97</v>
+        <v>26761.41</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0053916958837</v>
+        <v>0.0050879468724</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2888,25 +2808,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C49" s="13" t="s">
-        <v>116</v>
-      </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="F49" s="14">
-        <v>1723061</v>
+        <v>1238698</v>
       </c>
       <c r="G49" s="15">
-        <v>22155.98</v>
+        <v>24989.49</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0045776534141</v>
+        <v>0.0047510649659</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2917,25 +2837,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="D50" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D50" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>119</v>
-      </c>
       <c r="F50" s="14">
-        <v>7717819</v>
+        <v>3769076</v>
       </c>
       <c r="G50" s="15">
-        <v>20579.56</v>
+        <v>23666.03</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0042519488235</v>
+        <v>0.0044994454074</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2946,25 +2866,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="D51" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D51" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>56</v>
-      </c>
       <c r="F51" s="14">
-        <v>1722066</v>
+        <v>8078554</v>
       </c>
       <c r="G51" s="15">
-        <v>19213.95</v>
+        <v>22216.02</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0039697997478</v>
+        <v>0.0042237658433</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2984,16 +2904,16 @@
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="F52" s="14">
-        <v>1402724</v>
+        <v>4531047</v>
       </c>
       <c r="G52" s="15">
-        <v>18190.52</v>
+        <v>21642.55</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0037583485805</v>
+        <v>0.0041147362782</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -3013,16 +2933,16 @@
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="F53" s="14">
-        <v>4087531</v>
+        <v>1591349</v>
       </c>
       <c r="G53" s="15">
-        <v>17709.23</v>
+        <v>20111.47</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0036589091149</v>
+        <v>0.0038236434809</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -3042,16 +2962,16 @@
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="F54" s="14">
-        <v>868411</v>
+        <v>3161844</v>
       </c>
       <c r="G54" s="15">
-        <v>17434.65</v>
+        <v>20030.28</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0036021780619</v>
+        <v>0.003808207433</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -3062,25 +2982,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F55" s="14">
-        <v>2853188</v>
+        <v>14590756</v>
       </c>
       <c r="G55" s="15">
-        <v>17064.92</v>
+        <v>19029.26</v>
       </c>
       <c r="H55" s="16">
-        <v>0.00352578804</v>
+        <v>0.0036178909819</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3091,25 +3011,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F56" s="14">
-        <v>1044282</v>
+        <v>6768967</v>
       </c>
       <c r="G56" s="15">
-        <v>15922.69</v>
+        <v>16900.08</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0032897915705</v>
+        <v>0.0032130859016</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3120,25 +3040,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="F57" s="14">
-        <v>3500070</v>
+        <v>1044282</v>
       </c>
       <c r="G57" s="15">
-        <v>15449.31</v>
+        <v>16589.46</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0031919863922</v>
+        <v>0.0031540300426</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3149,25 +3069,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="F58" s="14">
-        <v>2767975</v>
+        <v>1854501</v>
       </c>
       <c r="G58" s="15">
-        <v>15383.02</v>
+        <v>16452.21</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0031782901962</v>
+        <v>0.0031279357259</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3178,25 +3098,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="F59" s="14">
-        <v>1484419</v>
+        <v>868411</v>
       </c>
       <c r="G59" s="15">
-        <v>14606.68</v>
+        <v>16350.44</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0030178903651</v>
+        <v>0.0031085869564</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3207,25 +3127,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="F60" s="14">
-        <v>783660</v>
+        <v>298639</v>
       </c>
       <c r="G60" s="15">
-        <v>14390.74</v>
+        <v>15226.11</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0029732749394</v>
+        <v>0.0028948264965</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3236,25 +3156,25 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D61" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F61" s="14">
-        <v>1442759</v>
+        <v>657985</v>
       </c>
       <c r="G61" s="15">
-        <v>14227.05</v>
+        <v>15173.79</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0029394549013</v>
+        <v>0.002884879286</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3274,16 +3194,16 @@
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="F62" s="14">
-        <v>18117738</v>
+        <v>119145</v>
       </c>
       <c r="G62" s="15">
-        <v>13793.03</v>
+        <v>14135.96</v>
       </c>
       <c r="H62" s="16">
-        <v>0.002849781904</v>
+        <v>0.0026875644247</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3303,16 +3223,16 @@
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>149</v>
+        <v>65</v>
       </c>
       <c r="F63" s="14">
-        <v>3087639</v>
+        <v>1484419</v>
       </c>
       <c r="G63" s="15">
-        <v>12223.96</v>
+        <v>13816.97</v>
       </c>
       <c r="H63" s="16">
-        <v>0.002525595899</v>
+        <v>0.00262691724</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3323,25 +3243,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C64" s="13" t="s">
-        <v>151</v>
-      </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="F64" s="14">
-        <v>11374156</v>
+        <v>1650000</v>
       </c>
       <c r="G64" s="15">
-        <v>12009.97</v>
+        <v>13479.68</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0024813833635</v>
+        <v>0.0025627908132</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3352,25 +3272,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F65" s="14">
-        <v>119145</v>
+        <v>18117738</v>
       </c>
       <c r="G65" s="15">
-        <v>11155.13</v>
+        <v>11546.43</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0023047646247</v>
+        <v>0.0021952364395</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3381,25 +3301,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F66" s="14">
         <v>1001956</v>
       </c>
       <c r="G66" s="15">
-        <v>10607.21</v>
+        <v>11409.77</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0021915587155</v>
+        <v>0.0021692542951</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3410,25 +3330,25 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="F67" s="14">
-        <v>925467</v>
+        <v>1087499</v>
       </c>
       <c r="G67" s="15">
-        <v>10092.22</v>
+        <v>9209.49</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0020851564832</v>
+        <v>0.0017509315033</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3439,25 +3359,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="F68" s="14">
-        <v>1073912</v>
+        <v>925467</v>
       </c>
       <c r="G68" s="15">
-        <v>7936.21</v>
+        <v>9118.16</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0016397026356</v>
+        <v>0.001733567613</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3468,25 +3388,25 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C69" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="D69" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>104</v>
-      </c>
       <c r="F69" s="14">
-        <v>1445508</v>
+        <v>458089</v>
       </c>
       <c r="G69" s="15">
-        <v>7025.17</v>
+        <v>8929.99</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0014514723986</v>
+        <v>0.0016977922572</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3497,25 +3417,25 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C70" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="D70" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="D70" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="F70" s="14">
-        <v>93575</v>
+        <v>2247639</v>
       </c>
       <c r="G70" s="15">
-        <v>4737.75</v>
+        <v>8929.87</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0009788678931</v>
+        <v>0.0016977694425</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3535,16 +3455,16 @@
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="F71" s="14">
-        <v>2450691</v>
+        <v>1090629</v>
       </c>
       <c r="G71" s="15">
-        <v>3993.40</v>
+        <v>6782.08</v>
       </c>
       <c r="H71" s="16">
-        <v>0.000825077525</v>
+        <v>0.0012894261821</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3555,25 +3475,25 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C72" s="13" t="s">
-        <v>169</v>
-      </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="F72" s="14">
-        <v>250000</v>
+        <v>1445508</v>
       </c>
       <c r="G72" s="15">
-        <v>2478</v>
+        <v>6650.06</v>
       </c>
       <c r="H72" s="16">
-        <v>0.0005119802942</v>
+        <v>0.0012643262062</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>13</v>
@@ -3584,25 +3504,25 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C73" s="13" t="s">
-        <v>171</v>
-      </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="F73" s="14">
-        <v>198954</v>
+        <v>903325</v>
       </c>
       <c r="G73" s="15">
-        <v>2385.96</v>
+        <v>3702.28</v>
       </c>
       <c r="H73" s="16">
-        <v>0.0004929638833</v>
+        <v>0.0007038868261</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>13</v>
@@ -3613,25 +3533,25 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C74" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>173</v>
-      </c>
       <c r="D74" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F74" s="14">
-        <v>903325</v>
+        <v>952478</v>
       </c>
       <c r="G74" s="15">
-        <v>2377.55</v>
+        <v>3613.23</v>
       </c>
       <c r="H74" s="16">
-        <v>0.0004912262908</v>
+        <v>0.0006869564151</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -3650,7 +3570,7 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>13</v>
@@ -3665,10 +3585,10 @@
         <v>13</v>
       </c>
       <c r="G76" s="9">
-        <v>158724.68</v>
+        <v>104034.39</v>
       </c>
       <c r="H76" s="10">
-        <v>0.0327941518864</v>
+        <v>0.0197792810328</v>
       </c>
       <c r="I76" s="9" t="s">
         <v>13</v>
@@ -3679,25 +3599,25 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C77" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="D77" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D77" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>177</v>
-      </c>
       <c r="F77" s="14">
-        <v>8771947</v>
+        <v>8686950</v>
       </c>
       <c r="G77" s="15">
-        <v>64905.18</v>
+        <v>65269.39</v>
       </c>
       <c r="H77" s="16">
-        <v>0.0134100779484</v>
+        <v>0.0124091813068</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>13</v>
@@ -3708,25 +3628,25 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C78" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="D78" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="D78" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>180</v>
-      </c>
       <c r="F78" s="14">
-        <v>5015365</v>
+        <v>4385973</v>
       </c>
       <c r="G78" s="15">
-        <v>49015.91</v>
+        <v>38765</v>
       </c>
       <c r="H78" s="16">
-        <v>0.0101271912937</v>
+        <v>0.007370099726</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>13</v>
@@ -3737,361 +3657,361 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15" customHeight="1">
+      <c r="B80" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="H80" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1">
+      <c r="B81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" ht="15" customHeight="1">
+      <c r="B82" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="D79" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E79" s="13" t="s">
+      <c r="C82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" ht="15" customHeight="1">
+      <c r="B83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15" customHeight="1">
+      <c r="B84" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" ht="15" customHeight="1">
+      <c r="B85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15" customHeight="1">
+      <c r="B86" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="F79" s="14">
-        <v>1304529</v>
-      </c>
-      <c r="G79" s="15">
-        <v>44803.59</v>
-      </c>
-      <c r="H79" s="16">
-        <v>0.0092568826443</v>
-      </c>
-      <c r="I79" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="7" t="s">
+      <c r="C86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15" customHeight="1">
+      <c r="B87" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" ht="15" customHeight="1">
+      <c r="B88" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="9" t="s">
+      <c r="C88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" ht="15" customHeight="1">
+      <c r="B89" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" ht="15" customHeight="1">
+      <c r="B90" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H81" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J82" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="7" t="s">
+      <c r="C90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J90" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" ht="15" customHeight="1">
+      <c r="B91" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J91" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" ht="15" customHeight="1">
+      <c r="B92" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" ht="15" customHeight="1">
-      <c r="B87" s="7" t="s">
+      <c r="C92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H92" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J92" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" ht="15" customHeight="1">
+      <c r="B93" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J93" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" ht="15" customHeight="1">
+      <c r="B94" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" ht="15" customHeight="1">
-      <c r="B88" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J88" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="7" t="s">
+      <c r="C94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="9">
+        <v>184088.15</v>
+      </c>
+      <c r="H94" s="10">
+        <v>0.034999304111100006</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J94" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" ht="15" customHeight="1">
+      <c r="B95" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J95" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" ht="15" customHeight="1">
+      <c r="B96" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J89" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10" ht="15" customHeight="1">
-      <c r="B90" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J90" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="7" t="s">
+      <c r="C96" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="9">
+        <v>29595.519999999997</v>
+      </c>
+      <c r="H96" s="10">
+        <v>0.005626775025</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J96" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" ht="15" customHeight="1">
+      <c r="B97" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J91" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J92" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="93" spans="2:10" ht="15" customHeight="1">
-      <c r="B93" s="7" t="s">
+      <c r="D97" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="C93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J93" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="94" spans="2:10" ht="15" customHeight="1">
-      <c r="B94" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J94" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10" ht="15" customHeight="1">
-      <c r="B95" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" s="9">
-        <v>192062.30000000002</v>
-      </c>
-      <c r="H95" s="10">
-        <v>0.03968204716340001</v>
-      </c>
-      <c r="I95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J95" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="96" spans="2:10" ht="15" customHeight="1">
-      <c r="B96" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J96" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="97" spans="2:10" ht="15" customHeight="1">
-      <c r="B97" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="9">
-        <v>79756.28</v>
-      </c>
-      <c r="H97" s="10">
-        <v>0.016478467999899996</v>
-      </c>
-      <c r="I97" s="9" t="s">
-        <v>13</v>
+      <c r="F97" s="14">
+        <v>5000</v>
+      </c>
+      <c r="G97" s="15">
+        <v>24598.10</v>
+      </c>
+      <c r="H97" s="16">
+        <v>0.0046766529104</v>
+      </c>
+      <c r="I97" s="15">
+        <v>6.28</v>
       </c>
       <c r="J97" s="11" t="s">
         <v>13</v>
@@ -4099,28 +4019,28 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D98" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F98" s="14">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="G98" s="15">
-        <v>29964.30</v>
+        <v>4997.42</v>
       </c>
       <c r="H98" s="16">
-        <v>0.00619093266</v>
+        <v>0.0009501221146</v>
       </c>
       <c r="I98" s="15">
-        <v>7.25</v>
+        <v>6.30</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>13</v>
@@ -4128,57 +4048,36 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="C99" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D99" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F99" s="14">
-        <v>3000</v>
-      </c>
-      <c r="G99" s="15">
-        <v>14943.21</v>
-      </c>
-      <c r="H99" s="16">
-        <v>0.0030874209254</v>
-      </c>
-      <c r="I99" s="15">
-        <v>7.30</v>
+        <v>13</v>
       </c>
       <c r="J99" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
-      <c r="B100" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="C100" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F100" s="14">
-        <v>2000</v>
-      </c>
-      <c r="G100" s="15">
-        <v>9988.01</v>
-      </c>
-      <c r="H100" s="16">
-        <v>0.002063625625</v>
-      </c>
-      <c r="I100" s="15">
-        <v>7.30</v>
+      <c r="B100" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="9">
+        <v>87427.03</v>
+      </c>
+      <c r="H100" s="10">
+        <v>0.016621847796899996</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>13</v>
@@ -4186,28 +4085,28 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="12" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D101" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F101" s="14">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="G101" s="15">
-        <v>9952.36</v>
+        <v>39965.32</v>
       </c>
       <c r="H101" s="16">
-        <v>0.0020562599683</v>
+        <v>0.0075983075966</v>
       </c>
       <c r="I101" s="15">
-        <v>7.28</v>
+        <v>6.34</v>
       </c>
       <c r="J101" s="11" t="s">
         <v>13</v>
@@ -4215,28 +4114,28 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
       <c r="B102" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D102" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F102" s="14">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="G102" s="15">
-        <v>9932.28</v>
+        <v>27489.74</v>
       </c>
       <c r="H102" s="16">
-        <v>0.0020521112337</v>
+        <v>0.0052264188119</v>
       </c>
       <c r="I102" s="15">
-        <v>7.32</v>
+        <v>6.82</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>13</v>
@@ -4244,28 +4143,28 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
       <c r="B103" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D103" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F103" s="14">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G103" s="15">
-        <v>4976.12</v>
+        <v>14979</v>
       </c>
       <c r="H103" s="16">
-        <v>0.0010281175875</v>
+        <v>0.0028478453191</v>
       </c>
       <c r="I103" s="15">
-        <v>7.30</v>
+        <v>6.40</v>
       </c>
       <c r="J103" s="11" t="s">
         <v>13</v>
@@ -4273,35 +4172,35 @@
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
       <c r="B104" s="12" t="s">
-        <v>13</v>
+        <v>200</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="F104" s="14">
+        <v>1000</v>
+      </c>
+      <c r="G104" s="15">
+        <v>4992.97</v>
+      </c>
+      <c r="H104" s="16">
+        <v>0.0009492760693</v>
+      </c>
+      <c r="I104" s="15">
+        <v>6.43</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
-      <c r="B105" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G105" s="9">
-        <v>59885.149999999994</v>
-      </c>
-      <c r="H105" s="10">
-        <v>0.012372888103</v>
-      </c>
-      <c r="I105" s="9" t="s">
+      <c r="B105" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J105" s="11" t="s">
@@ -4309,29 +4208,29 @@
       </c>
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
-      <c r="B106" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="C106" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F106" s="14">
-        <v>4000</v>
-      </c>
-      <c r="G106" s="15">
-        <v>19975.76</v>
-      </c>
-      <c r="H106" s="16">
-        <v>0.0041271975315</v>
-      </c>
-      <c r="I106" s="15">
-        <v>7.38</v>
+      <c r="B106" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="9">
+        <v>67065.6</v>
+      </c>
+      <c r="H106" s="10">
+        <v>0.012750681289199999</v>
+      </c>
+      <c r="I106" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>13</v>
@@ -4339,28 +4238,28 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
       <c r="B107" s="12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D107" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="F107" s="14">
-        <v>4000</v>
+        <v>15000000</v>
       </c>
       <c r="G107" s="15">
-        <v>19974.66</v>
+        <v>14974.28</v>
       </c>
       <c r="H107" s="16">
-        <v>0.0041269702602</v>
+        <v>0.0028469479408</v>
       </c>
       <c r="I107" s="15">
-        <v>7.72</v>
+        <v>5.70</v>
       </c>
       <c r="J107" s="11" t="s">
         <v>13</v>
@@ -4368,28 +4267,28 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
       <c r="B108" s="12" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D108" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="F108" s="14">
-        <v>2000</v>
+        <v>15000000</v>
       </c>
       <c r="G108" s="15">
-        <v>9965.93</v>
+        <v>14847.03</v>
       </c>
       <c r="H108" s="16">
-        <v>0.0020590636699</v>
+        <v>0.0028227548493</v>
       </c>
       <c r="I108" s="15">
-        <v>7.34</v>
+        <v>5.61</v>
       </c>
       <c r="J108" s="11" t="s">
         <v>13</v>
@@ -4397,28 +4296,28 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
       <c r="B109" s="12" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D109" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="F109" s="14">
-        <v>1000</v>
+        <v>12500000</v>
       </c>
       <c r="G109" s="15">
-        <v>4989.91</v>
+        <v>12384.09</v>
       </c>
       <c r="H109" s="16">
-        <v>0.0010309667434</v>
+        <v>0.0023544944748</v>
       </c>
       <c r="I109" s="15">
-        <v>7.38</v>
+        <v>5.60</v>
       </c>
       <c r="J109" s="11" t="s">
         <v>13</v>
@@ -4426,28 +4325,28 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="12" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D110" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="F110" s="14">
-        <v>1000</v>
+        <v>10000000</v>
       </c>
       <c r="G110" s="15">
-        <v>4978.89</v>
+        <v>9939</v>
       </c>
       <c r="H110" s="16">
-        <v>0.001028689898</v>
+        <v>0.0018896277873</v>
       </c>
       <c r="I110" s="15">
-        <v>7.74</v>
+        <v>5.60</v>
       </c>
       <c r="J110" s="11" t="s">
         <v>13</v>
@@ -4455,36 +4354,57 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
       <c r="B111" s="12" t="s">
-        <v>13</v>
+        <v>203</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="F111" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="G111" s="15">
+        <v>9929.77</v>
+      </c>
+      <c r="H111" s="16">
+        <v>0.0018878729564</v>
+      </c>
+      <c r="I111" s="15">
+        <v>5.61</v>
       </c>
       <c r="J111" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="9">
-        <v>52420.87000000001</v>
-      </c>
-      <c r="H112" s="10">
-        <v>0.0108306910605</v>
-      </c>
-      <c r="I112" s="9" t="s">
-        <v>13</v>
+      <c r="B112" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="F112" s="14">
+        <v>5000000</v>
+      </c>
+      <c r="G112" s="15">
+        <v>4991.43</v>
+      </c>
+      <c r="H112" s="16">
+        <v>0.0009489832806</v>
+      </c>
+      <c r="I112" s="15">
+        <v>5.70</v>
       </c>
       <c r="J112" s="11" t="s">
         <v>13</v>
@@ -4492,57 +4412,36 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
       <c r="B113" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="C113" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="D113" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F113" s="14">
-        <v>20000000</v>
-      </c>
-      <c r="G113" s="15">
-        <v>19808.22</v>
-      </c>
-      <c r="H113" s="16">
-        <v>0.0040925820438</v>
-      </c>
-      <c r="I113" s="15">
-        <v>6.43</v>
+        <v>13</v>
       </c>
       <c r="J113" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
-      <c r="B114" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="C114" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="D114" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E114" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F114" s="14">
-        <v>12150000</v>
-      </c>
-      <c r="G114" s="15">
-        <v>11989.44</v>
-      </c>
-      <c r="H114" s="16">
-        <v>0.0024771416543</v>
-      </c>
-      <c r="I114" s="15">
-        <v>6.52</v>
+      <c r="B114" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H114" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I114" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J114" s="11" t="s">
         <v>13</v>
@@ -4550,57 +4449,36 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
       <c r="B115" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="C115" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F115" s="14">
-        <v>6600000</v>
-      </c>
-      <c r="G115" s="15">
-        <v>6520.77</v>
-      </c>
-      <c r="H115" s="16">
-        <v>0.0013472581692</v>
-      </c>
-      <c r="I115" s="15">
-        <v>6.52</v>
+        <v>13</v>
       </c>
       <c r="J115" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
-      <c r="B116" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C116" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="D116" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F116" s="14">
-        <v>5000000</v>
-      </c>
-      <c r="G116" s="15">
-        <v>4995.65</v>
-      </c>
-      <c r="H116" s="16">
-        <v>0.0010321526864</v>
-      </c>
-      <c r="I116" s="15">
-        <v>6.37</v>
+      <c r="B116" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I116" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J116" s="11" t="s">
         <v>13</v>
@@ -4608,57 +4486,36 @@
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
       <c r="B117" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="C117" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F117" s="14">
-        <v>5000000</v>
-      </c>
-      <c r="G117" s="15">
-        <v>4927.89</v>
-      </c>
-      <c r="H117" s="16">
-        <v>0.0010181527733</v>
-      </c>
-      <c r="I117" s="15">
-        <v>6.51</v>
+        <v>13</v>
       </c>
       <c r="J117" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
-      <c r="B118" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C118" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F118" s="14">
-        <v>4000000</v>
-      </c>
-      <c r="G118" s="15">
-        <v>3981.78</v>
-      </c>
-      <c r="H118" s="16">
-        <v>0.0008226767135</v>
-      </c>
-      <c r="I118" s="15">
-        <v>6.43</v>
+      <c r="B118" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="9">
+        <v>169058.58</v>
+      </c>
+      <c r="H118" s="10">
+        <v>0.0321418442964</v>
+      </c>
+      <c r="I118" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J118" s="11" t="s">
         <v>13</v>
@@ -4666,35 +4523,35 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
       <c r="B119" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C119" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="D119" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F119" s="14">
-        <v>200000</v>
-      </c>
-      <c r="G119" s="15">
-        <v>197.12</v>
-      </c>
-      <c r="H119" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="I119" s="15">
-        <v>6.51</v>
+        <v>13</v>
       </c>
       <c r="J119" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
-      <c r="B120" s="12" t="s">
+      <c r="B120" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" s="9">
+        <v>7625.000000499999</v>
+      </c>
+      <c r="H120" s="10">
+        <v>0.0014496842619</v>
+      </c>
+      <c r="I120" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J120" s="11" t="s">
@@ -4702,28 +4559,21 @@
       </c>
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
-      <c r="B121" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F121" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G121" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I121" s="9" t="s">
+      <c r="B121" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C121" s="13"/>
+      <c r="D121" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" s="13"/>
+      <c r="G121" s="15">
+        <v>7625.000000499999</v>
+      </c>
+      <c r="H121" s="16">
+        <v>0.0014496842619</v>
+      </c>
+      <c r="I121" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J121" s="11" t="s">
@@ -4739,545 +4589,220 @@
       </c>
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1">
-      <c r="B123" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G123" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I123" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J123" s="11" t="s">
+      <c r="B123" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="C123" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D123" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" s="18">
+        <v>16143.105979319662</v>
+      </c>
+      <c r="H123" s="19">
+        <v>0.003069168088650063</v>
+      </c>
+      <c r="I123" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J123" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1">
-      <c r="B124" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J124" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="125" spans="2:10" ht="15" customHeight="1">
-      <c r="B125" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D125" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F125" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G125" s="9">
-        <v>126738.70</v>
-      </c>
-      <c r="H125" s="10">
-        <v>0.0261855193388</v>
-      </c>
-      <c r="I125" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J125" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" ht="15" customHeight="1">
-      <c r="B126" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J126" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="2:10" ht="15" customHeight="1">
-      <c r="B127" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D127" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F127" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G127" s="9">
-        <v>18140.0000005</v>
-      </c>
-      <c r="H127" s="10">
-        <v>0.0037479106288</v>
-      </c>
-      <c r="I127" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J127" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="128" spans="2:10" ht="15" customHeight="1">
-      <c r="B128" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="C128" s="13"/>
-      <c r="D128" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E128" s="13"/>
-      <c r="G128" s="15">
-        <v>18140.0000005</v>
-      </c>
-      <c r="H128" s="16">
-        <v>0.0037479106288</v>
-      </c>
-      <c r="I128" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J128" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="129" spans="2:10" ht="15" customHeight="1">
-      <c r="B129" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J129" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10" ht="15" customHeight="1">
-      <c r="B130" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="C130" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D130" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E130" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F130" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G130" s="19">
-        <v>-4907.208134519868</v>
-      </c>
-      <c r="H130" s="20">
-        <v>-0.0010138796871530958</v>
-      </c>
-      <c r="I130" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J130" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10" ht="15" customHeight="1">
-      <c r="B131" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C131" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D131" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E131" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F131" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G131" s="19">
-        <v>4840030.03186598</v>
-      </c>
-      <c r="H131" s="20">
-        <v>0.9999999999958469</v>
-      </c>
-      <c r="I131" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J131" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="133" spans="2:8" ht="15" customHeight="1">
-      <c r="B133" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="C133" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D133" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E133" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F133" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G133" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H133" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="134" spans="2:8" ht="15" customHeight="1">
-      <c r="B134" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C134" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D134" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E134" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F134" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G134" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="H134" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="135" spans="2:8" ht="15" customHeight="1">
-      <c r="B135" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D135" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E135" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F135" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H135" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="136" spans="2:10" ht="15" customHeight="1">
-      <c r="B136" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="C136" s="13"/>
-      <c r="D136" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E136" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="F136" s="14">
-        <v>255000</v>
-      </c>
-      <c r="G136" s="15">
-        <v>3320.74</v>
-      </c>
-      <c r="H136" s="16">
-        <v>0.0006860990485</v>
-      </c>
-      <c r="I136" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J136" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="137" spans="2:10" ht="15" customHeight="1">
-      <c r="B137" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="C137" s="13"/>
-      <c r="D137" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E137" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F137" s="14">
-        <v>250000</v>
-      </c>
-      <c r="G137" s="15">
-        <v>2495</v>
-      </c>
-      <c r="H137" s="16">
-        <v>0.0005154926691</v>
-      </c>
-      <c r="I137" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J137" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="138" spans="2:10" ht="15" customHeight="1">
-      <c r="B138" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="C138" s="13"/>
-      <c r="D138" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E138" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F138" s="14">
-        <v>21600</v>
-      </c>
-      <c r="G138" s="15">
-        <v>168.40</v>
-      </c>
-      <c r="H138" s="17" t="s">
+      <c r="B124" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="C124" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G124" s="18">
+        <v>5259766.00597982</v>
+      </c>
+      <c r="H124" s="19">
+        <v>0.99999999999575</v>
+      </c>
+      <c r="I124" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J124" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="2:9" ht="15" customHeight="1">
+      <c r="B127" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C127" s="21"/>
+      <c r="D127" s="21"/>
+      <c r="E127" s="21"/>
+      <c r="F127" s="21"/>
+      <c r="G127" s="21"/>
+      <c r="H127" s="21"/>
+      <c r="I127" s="21"/>
+    </row>
+    <row r="128" spans="2:8" ht="15" customHeight="1">
+      <c r="B128" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="C128" s="21"/>
+      <c r="D128" s="21"/>
+      <c r="E128" s="21"/>
+      <c r="F128" s="21"/>
+      <c r="G128" s="21"/>
+      <c r="H128" s="21"/>
+    </row>
+    <row r="130" spans="2:8" ht="15" customHeight="1">
+      <c r="B130" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C130" s="21"/>
+      <c r="D130" s="21"/>
+      <c r="E130" s="21"/>
+      <c r="F130" s="21"/>
+      <c r="G130" s="21"/>
+      <c r="H130" s="21"/>
+    </row>
+    <row r="132" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B132" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="C132" s="23"/>
+      <c r="D132" s="23"/>
+      <c r="E132" s="23"/>
+      <c r="F132" s="23"/>
+      <c r="G132" s="23"/>
+      <c r="H132" s="23"/>
+    </row>
+    <row r="133" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B133" s="23"/>
+      <c r="C133" s="23"/>
+      <c r="D133" s="23"/>
+      <c r="E133" s="23"/>
+      <c r="F133" s="23"/>
+      <c r="G133" s="23"/>
+      <c r="H133" s="23"/>
+    </row>
+    <row r="134" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B134" s="23"/>
+      <c r="C134" s="23"/>
+      <c r="D134" s="23"/>
+      <c r="E134" s="23"/>
+      <c r="F134" s="23"/>
+      <c r="G134" s="23"/>
+      <c r="H134" s="23"/>
+    </row>
+    <row r="135" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B135" s="23"/>
+      <c r="C135" s="23"/>
+      <c r="D135" s="23"/>
+      <c r="E135" s="23"/>
+      <c r="F135" s="23"/>
+      <c r="G135" s="23"/>
+      <c r="H135" s="23"/>
+    </row>
+    <row r="136" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B136" s="23"/>
+      <c r="C136" s="23"/>
+      <c r="D136" s="23"/>
+      <c r="E136" s="23"/>
+      <c r="F136" s="23"/>
+      <c r="G136" s="23"/>
+      <c r="H136" s="23"/>
+    </row>
+    <row r="137" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B137" s="23"/>
+      <c r="C137" s="23"/>
+      <c r="D137" s="23"/>
+      <c r="E137" s="23"/>
+      <c r="F137" s="23"/>
+      <c r="G137" s="23"/>
+      <c r="H137" s="23"/>
+    </row>
+    <row r="139" spans="2:8" ht="15" customHeight="1">
+      <c r="B139" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C139" s="21"/>
+      <c r="D139" s="21"/>
+      <c r="E139" s="21"/>
+      <c r="F139" s="21"/>
+      <c r="G139" s="21"/>
+      <c r="H139" s="21"/>
+    </row>
+    <row r="140" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B140" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="C140" s="21"/>
+      <c r="D140" s="21"/>
+      <c r="E140" s="21"/>
+      <c r="F140" s="21"/>
+      <c r="G140" s="21"/>
+      <c r="H140" s="21"/>
+    </row>
+    <row r="141" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B141" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="C141" s="21"/>
+      <c r="D141" s="21"/>
+      <c r="E141" s="21"/>
+      <c r="F141" s="21"/>
+      <c r="G141" s="21"/>
+      <c r="H141" s="21"/>
+    </row>
+    <row r="142" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B142" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="C142" s="21"/>
+      <c r="D142" s="21"/>
+      <c r="E142" s="21"/>
+      <c r="F142" s="21"/>
+      <c r="G142" s="21"/>
+      <c r="H142" s="21"/>
+    </row>
+    <row r="145" ht="15">
+      <c r="B145" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="I138" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J138" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="142" spans="2:9" ht="15" customHeight="1">
-      <c r="B142" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="C142" s="22"/>
-      <c r="D142" s="22"/>
-      <c r="E142" s="22"/>
-      <c r="F142" s="22"/>
-      <c r="G142" s="22"/>
-      <c r="H142" s="22"/>
-      <c r="I142" s="22"/>
-    </row>
-    <row r="146" spans="2:9" ht="15" customHeight="1">
-      <c r="B146" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="C146" s="22"/>
-      <c r="D146" s="22"/>
-      <c r="E146" s="22"/>
-      <c r="F146" s="22"/>
-      <c r="G146" s="22"/>
-      <c r="H146" s="22"/>
-      <c r="I146" s="22"/>
-    </row>
-    <row r="147" spans="2:8" ht="15" customHeight="1">
-      <c r="B147" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="C147" s="22"/>
-      <c r="D147" s="22"/>
-      <c r="E147" s="22"/>
-      <c r="F147" s="22"/>
-      <c r="G147" s="22"/>
-      <c r="H147" s="22"/>
-    </row>
-    <row r="148" spans="2:8" ht="15" customHeight="1">
-      <c r="B148" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="C148" s="22"/>
-      <c r="D148" s="22"/>
-      <c r="E148" s="22"/>
-      <c r="F148" s="22"/>
-      <c r="G148" s="22"/>
-      <c r="H148" s="22"/>
-    </row>
-    <row r="149" spans="2:8" ht="15" customHeight="1">
-      <c r="B149" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="C149" s="22"/>
-      <c r="D149" s="22"/>
-      <c r="E149" s="22"/>
-      <c r="F149" s="22"/>
-      <c r="G149" s="22"/>
-      <c r="H149" s="22"/>
-    </row>
-    <row r="151" spans="2:8" ht="15" customHeight="1">
-      <c r="B151" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="C151" s="22"/>
-      <c r="D151" s="22"/>
-      <c r="E151" s="22"/>
-      <c r="F151" s="22"/>
-      <c r="G151" s="22"/>
-      <c r="H151" s="22"/>
-    </row>
-    <row r="153" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B153" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="C153" s="24"/>
-      <c r="D153" s="24"/>
-      <c r="E153" s="24"/>
-      <c r="F153" s="24"/>
-      <c r="G153" s="24"/>
-      <c r="H153" s="24"/>
-    </row>
-    <row r="154" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B154" s="24"/>
-      <c r="C154" s="24"/>
-      <c r="D154" s="24"/>
-      <c r="E154" s="24"/>
-      <c r="F154" s="24"/>
-      <c r="G154" s="24"/>
-      <c r="H154" s="24"/>
-    </row>
-    <row r="155" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B155" s="24"/>
-      <c r="C155" s="24"/>
-      <c r="D155" s="24"/>
-      <c r="E155" s="24"/>
-      <c r="F155" s="24"/>
-      <c r="G155" s="24"/>
-      <c r="H155" s="24"/>
-    </row>
-    <row r="156" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B156" s="24"/>
-      <c r="C156" s="24"/>
-      <c r="D156" s="24"/>
-      <c r="E156" s="24"/>
-      <c r="F156" s="24"/>
-      <c r="G156" s="24"/>
-      <c r="H156" s="24"/>
-    </row>
-    <row r="157" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B157" s="24"/>
-      <c r="C157" s="24"/>
-      <c r="D157" s="24"/>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="24"/>
-      <c r="H157" s="24"/>
-    </row>
-    <row r="158" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B158" s="24"/>
-      <c r="C158" s="24"/>
-      <c r="D158" s="24"/>
-      <c r="E158" s="24"/>
-      <c r="F158" s="24"/>
-      <c r="G158" s="24"/>
-      <c r="H158" s="24"/>
-    </row>
-    <row r="160" spans="2:8" ht="15" customHeight="1">
-      <c r="B160" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C160" s="22"/>
-      <c r="D160" s="22"/>
-      <c r="E160" s="22"/>
-      <c r="F160" s="22"/>
-      <c r="G160" s="22"/>
-      <c r="H160" s="22"/>
-    </row>
-    <row r="161" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B161" s="25" t="s">
-        <v>248</v>
-      </c>
-      <c r="C161" s="22"/>
-      <c r="D161" s="22"/>
-      <c r="E161" s="22"/>
-      <c r="F161" s="22"/>
-      <c r="G161" s="22"/>
-      <c r="H161" s="22"/>
-    </row>
-    <row r="162" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B162" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="C162" s="22"/>
-      <c r="D162" s="22"/>
-      <c r="E162" s="22"/>
-      <c r="F162" s="22"/>
-      <c r="G162" s="22"/>
-      <c r="H162" s="22"/>
-    </row>
-    <row r="163" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B163" s="25" t="s">
-        <v>250</v>
-      </c>
-      <c r="C163" s="22"/>
-      <c r="D163" s="22"/>
-      <c r="E163" s="22"/>
-      <c r="F163" s="22"/>
-      <c r="G163" s="22"/>
-      <c r="H163" s="22"/>
-    </row>
-    <row r="166" ht="15">
-      <c r="B166" s="22" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="181" ht="15">
-      <c r="B181" s="22" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="182" ht="15">
-      <c r="B182" s="22" t="s">
-        <v>253</v>
+    </row>
+    <row r="160" ht="15">
+      <c r="B160" s="21" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B160:H160"/>
-    <mergeCell ref="B161:H161"/>
-    <mergeCell ref="B162:H162"/>
-    <mergeCell ref="B163:H163"/>
-    <mergeCell ref="B147:H147"/>
-    <mergeCell ref="B148:H148"/>
-    <mergeCell ref="B149:H149"/>
-    <mergeCell ref="B151:H151"/>
-    <mergeCell ref="B153:H158"/>
+  <mergeCells count="11">
+    <mergeCell ref="B142:H142"/>
+    <mergeCell ref="B130:H130"/>
+    <mergeCell ref="B132:H137"/>
+    <mergeCell ref="B139:H139"/>
+    <mergeCell ref="B140:H140"/>
+    <mergeCell ref="B141:H141"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B142:I142"/>
-    <mergeCell ref="B146:I146"/>
+    <mergeCell ref="B127:I127"/>
+    <mergeCell ref="B128:H128"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
